--- a/datasets/20261020_recontrataciones_aguascalientes.xlsx
+++ b/datasets/20261020_recontrataciones_aguascalientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INE\Documents\reductor_dias\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7375BEFD-F3DF-4085-A188-03958946AD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31896965-F1F7-4608-BC11-039FC3811EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3C7E6B5-2A0E-4AF2-BE80-0C96F41EC4B0}"/>
   </bookViews>
